--- a/results/case_0001/design_results.xlsx
+++ b/results/case_0001/design_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,90 +454,130 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>VRebar_req_units</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>TTrnRebar_req</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>TTrnRebar_req_units</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>TLngRebar_req</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>TLngRebar_req_units</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>E_bar</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>G_bar</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>G_count</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>spacing_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>controlling_limit</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Av1</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Av2</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Av_total</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>At</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>At_over_s</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Av_over_s</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>long_bar</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>long_count</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>long_provided_mm2</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>check_torsion</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>check_shear</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>check_longitudinal</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>check_detailing</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>failure_mode</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>message</t>
         </is>
@@ -575,70 +615,100 @@
       <c r="G2" t="n">
         <v>1492.33</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>mm2/m</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>1115.53</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mm2/m</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>2727</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>mm2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>2</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>100</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>d/4</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>34.894</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>142</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>176.894</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>129</v>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>1290</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
         <v>1768.94</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="Y2" t="n">
         <v>14</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="n">
+        <v>2786</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Candidate satisfies torsion, shear, and detailing checks</t>
         </is>
@@ -676,70 +746,100 @@
       <c r="G3" t="n">
         <v>1495.83</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>mm2/m</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>685.65</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mm2/m</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>1721</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>mm2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="O3" t="n">
         <v>4</v>
       </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
         <v>180</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Ph/8</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>11.16600000000001</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>284</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>295.166</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>129</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>716.6666666666666</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>1639.811111111111</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="Y3" t="n">
         <v>14</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="n">
+        <v>1806</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Candidate satisfies torsion, shear, and detailing checks</t>
         </is>
@@ -777,70 +877,100 @@
       <c r="G4" t="n">
         <v>2086.39</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>mm2/m</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>784.53</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mm2/m</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>1918</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>mm2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
         <v>140</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>d/4</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>38.33160000000002</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>258</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>296.3316</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>129</v>
       </c>
-      <c r="S4" t="n">
+      <c r="V4" t="n">
         <v>921.4285714285714</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>2116.654285714286</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="Y4" t="n">
         <v>10</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="n">
+        <v>1990</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Candidate satisfies torsion, shear, and detailing checks</t>
         </is>
